--- a/scratch/test_output_L3.xlsx
+++ b/scratch/test_output_L3.xlsx
@@ -584,19 +584,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="3.1640625" customWidth="1" style="1" min="1" max="1"/>
     <col width="2.6640625" customWidth="1" style="1" min="3" max="3"/>
     <col width="22.5" customWidth="1" style="1" min="4" max="4"/>
-    <col width="4.5" customWidth="1" style="1" min="5" max="5"/>
-    <col width="14.1640625" customWidth="1" style="1" min="6" max="6"/>
-    <col width="23" customWidth="1" style="1" min="7" max="7"/>
-    <col width="6.5" customWidth="1" style="2" min="8" max="9"/>
-    <col width="6.5" customWidth="1" style="3" min="10" max="11"/>
-    <col width="10.83203125" customWidth="1" style="2" min="12" max="12"/>
-    <col width="10.83203125" customWidth="1" style="1" min="13" max="16384"/>
+    <col width="4.5" customWidth="1" style="1" min="5" max="6"/>
+    <col width="14.1640625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="23" customWidth="1" style="1" min="8" max="8"/>
+    <col width="6.5" customWidth="1" style="2" min="9" max="9"/>
+    <col width="4.5" customWidth="1" style="1" min="10" max="11"/>
+    <col width="14.1640625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="23" customWidth="1" style="1" min="13" max="13"/>
+    <col width="6.5" customWidth="1" style="2" min="14" max="14"/>
+    <col width="6.5" customWidth="1" style="3" min="15" max="16"/>
+    <col width="10.83203125" customWidth="1" style="2" min="17" max="17"/>
+    <col width="10.83203125" customWidth="1" style="1" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,42 +611,72 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>units_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>data_type</t>
+          <t>sig_figs_1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>data_key</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
+          <t>data_type_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>data_key_1</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>4R1</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>units_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>sig_figs_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>data_type_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>data_key_1</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>4R2</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>4R3</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>3R2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" thickBot="1">
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>stove_type/model</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>stove_type/model</t>
         </is>
@@ -663,11 +697,11 @@
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
-      <c r="H4" s="9" t="n"/>
       <c r="I4" s="9" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="11" t="n"/>
@@ -676,32 +710,21 @@
           <t>Cold start</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +734,18 @@
           <t>High power</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -724,7 +758,18 @@
           <t>Medium power</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -737,7 +782,18 @@
           <t>Low power</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -750,11 +806,11 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="11" t="n"/>
@@ -795,11 +851,11 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="9" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="11" t="n"/>
@@ -808,39 +864,30 @@
           <t>Cold start</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_L1</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>average (N)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>17.5 (7)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17.5 (7)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>17.5 (26)</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>17.5 (4)</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_1_L1</t>
         </is>
       </c>
     </row>
@@ -851,39 +898,30 @@
           <t>High power</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_hp</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>average (N)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>17.5 (7)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17.5 (7)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>17.5 (26)</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>17.5 (4)</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_1_hp</t>
         </is>
       </c>
     </row>
@@ -894,14 +932,30 @@
           <t>Medium power</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>average (N)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>fuel_dry_mass_mp</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>average (N)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_1_mp</t>
         </is>
       </c>
     </row>
@@ -912,14 +966,30 @@
           <t>Low power</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>average (N)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>fuel_dry_mass_lp</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>average (N)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_1_lp</t>
         </is>
       </c>
     </row>
@@ -930,12 +1000,28 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>average</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>fuel_dry_mass_total</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
         <is>
           <t>fuel_dry_mass_total</t>
         </is>
@@ -948,11 +1034,11 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="11" t="n"/>
@@ -961,39 +1047,24 @@
           <t>Cold start</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_L1</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>average +- confidence (N)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (7)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (7)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (26)</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (4)</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_L1</t>
         </is>
       </c>
     </row>
@@ -1004,39 +1075,24 @@
           <t>High power</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_hp</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>average +- confidence (N)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (7)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (7)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (26)</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0 (4)</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_hp</t>
         </is>
       </c>
     </row>
@@ -1047,39 +1103,29 @@
           <t>Medium power</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>confidence (N)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>fuel_mc_1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.0 (7)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0 (7)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0.0 (26)</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.0 (4)</t>
+          <t>initial_fuel_mass_1_mp</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>average +- confidence</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_mp</t>
         </is>
       </c>
     </row>
@@ -1090,32 +1136,30 @@
           <t>Low power</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>fuel_mc_1</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_lp</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>average +- confidence</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>initial_fuel_mass_1_lp</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1134,7 +1178,9 @@
       </c>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="C27" s="11" t="n"/>
@@ -1148,34 +1194,29 @@
           <t>g/min</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_L1</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>g/min</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_L1</t>
         </is>
       </c>
     </row>
@@ -1191,34 +1232,29 @@
           <t>g/min</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_hp</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>g/min</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_hp</t>
         </is>
       </c>
     </row>
@@ -1234,34 +1270,29 @@
           <t>g/min</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_mp</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>g/min</t>
+        </is>
+      </c>
+      <c r="L29" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_mp</t>
         </is>
       </c>
     </row>
@@ -1277,34 +1308,29 @@
           <t>g/min</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_lp</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>g/min</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_lp</t>
         </is>
       </c>
     </row>
@@ -1324,6 +1350,7 @@
       </c>
       <c r="D32" s="13" t="n"/>
       <c r="E32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="C33" s="11" t="n"/>
@@ -1337,34 +1364,29 @@
           <t>lb/hr</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_L1</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_L1</t>
         </is>
       </c>
     </row>
@@ -1380,34 +1402,29 @@
           <t>lb/hr</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_hp</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_hp</t>
         </is>
       </c>
     </row>
@@ -1423,34 +1440,29 @@
           <t>lb/hr</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_mp</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_mp</t>
         </is>
       </c>
     </row>
@@ -1466,34 +1478,29 @@
           <t>lb/hr</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>fuel_mc_1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_lp</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
         <is>
           <t>average +- confidence</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>fuel_mc_1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>17.5 ± 0.0</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>burn_rate_dry_lp</t>
         </is>
       </c>
     </row>
